--- a/Result/checksun_type/製造商.xlsx
+++ b/Result/checksun_type/製造商.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>44.47000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>44.29</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>44.75</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>44.75</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>456.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>206.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>206.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>173.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1.638829260897808</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>456</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>456.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>44.5</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>44.29</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>44.77</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>44.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>46.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>115.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>115.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>141.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-28.29110368225724</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>46</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>44.25</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>44.28</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>44.78</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>44.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>45.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>152</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>220.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-21.42681343840434</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>45</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>44.12</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>44.28</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>44.78</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>352.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>152.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>152.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>223.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-10.74829832438579</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>352</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>44.13</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>44.82</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>133.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>110.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>110.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>203.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-28.00226607848836</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>133</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>44.1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>44.34</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>44.88</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>140.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>140.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>198.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-28.18642479583173</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>43.94</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>44.94</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>44.94</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>227.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>167.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>167.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>215.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-13.51427922075683</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>227</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>227.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>43.73</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>45.01</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>45.01</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>49.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>289.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>289.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>285.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-16.07141842705138</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>49</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>43.94</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>44.43</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>45.05</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>45.05</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>139.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>295.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>295</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>294.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-0.07906663507748135</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>139</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>43.87</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>44.47</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.12</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>286.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>296.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>296.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>316.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>13.12711687613802</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>286</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>286.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>44.33</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>44.54</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.19</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.19</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>135.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>255.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>255.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>302.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>15.77426771801237</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>135</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>49.11</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>48.38</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>48.89</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>48.89</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1901.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2664.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2664.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>3331.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>4424.76</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>4424.76</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-312.2036753926732</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1901</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1901.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>49.07</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>48.3</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>48.91</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>48.91</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>3105.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2481.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2481.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>3347.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>4528.48</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>4528.48</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-244.0282134059335</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>3105</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>3105.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>49.1</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>48.24</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>48.93</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>48.93</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2694.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2401.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2401.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>3133.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>4692.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>4692.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-266.9194029460928</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2694</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2694.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>49.06</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>48.17</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>48.94</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>48.94</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3028.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2987.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2987</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3197.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>4786.56</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>4786.56</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-246.0525521839604</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3028</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3028.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>48.97</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>48.13</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>48.96</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>48.96</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2596.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>4017.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>4017</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>4832.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>4864.14</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>4864.14</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-243.2408885172017</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2596</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2596.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,21 +7937,17 @@
           <t>48.78</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>48.09</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AM18" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="AO18" t="inlineStr">
         <is>
           <t>48.98</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
-      </c>
       <c r="AP18" t="inlineStr">
         <is>
           <t>97.92</t>
@@ -8088,20 +7988,16 @@
           <t>985.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>3998.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>3998.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>4804.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>4902.44</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>4902.44</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-184.2513372605035</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>985</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>985.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>48.62</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>48.08</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>49.01</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>49.01</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>2706.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>4212.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>4212.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>4822.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>4973.14</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>4973.14</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>79.20699800836974</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2706</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2706.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>48.42</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>48.06</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>49.03</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>49.03</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>5620.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>3866.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>3866</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>4656.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5022.5</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5022.5</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>268.3543698921758</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>5620</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>5620.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>48.26000000000001</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>49.05</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>49.05</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>8178.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3408.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>3408.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>4325.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5019.58</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5019.58</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>216.7665308014639</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>8178</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>8178.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>48.16</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>48.06</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>49.08</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>49.08</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>2503.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>5648.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>5648</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>3863.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>4939.08</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>4939.08</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-138.7434725710341</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2503</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2503.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>48.02</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>48.09</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>49.12</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>49.12</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2056.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>5609.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>5609.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>3734.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>5046.18</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>5046.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-33.62406765420883</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2056</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2056.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>7.604000000000001</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>7.59</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>7.81</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>7.81</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1017380.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1430733.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1430733.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2279081.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>3418238.5</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>3418238.5</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-496332.8317277101</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1017380</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1017380.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>7.556</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>7.59</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>7.81</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>7.81</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1621024.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1662415.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1662415</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>3035599.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>3472828.86</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>3472828.86</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-452941.2435561991</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1621024</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1621024.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>7.52</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>7.81</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>7.81</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1664903.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1952198.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1952198.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>3264464.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>3476886.2</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>3476886.2</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-439452.9303270332</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1664903</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1664903.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>7.536</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>7.82</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>7.82</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1340477.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>2072421.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>2072421.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3332847.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>3585342.66</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>3585342.66</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-409190.4853451164</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1340477</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1340477.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>7.63</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>7.83</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>7.83</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1509885.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>2939404.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>2939404</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3476218.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>3583057.04</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>3583057.04</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-316584.5466086236</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1509885</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1509885.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>7.640000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>7.84</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>7.84</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2175786.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>3127430.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>3127430</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3512324.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>3589303.96</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>3589303.96</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-191134.6146061835</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2175786</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2175786.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>7.678</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>7.67</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>7.85</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>3069941.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>4408784.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>4408784</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3724214.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>3607862.04</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>3607862.04</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-76440.7255096198</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>3069941</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>3069941.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>7.686</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>7.86</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>7.86</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>2266019.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4576729.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>4576729.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3687671.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>3578098.6</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>3578098.6</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-5664.608032042161</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>2266019</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>2266019.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>7.644</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>7.71</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>7.86</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>7.86</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>5675389.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>4593273.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>4593273</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>4305757.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>3582388.24</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>3582388.24</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>181780.9386513559</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>5675389</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>5675389.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>7.596000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>7.86</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>7.86</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>2450015.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>4013032.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>4013032.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>4492723.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>3488527.72</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>3488527.72</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>77778.47181866132</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>2450015</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>2450015.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,21 +14817,17 @@
           <t>7.55</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
+      <c r="AM34" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AO34" t="inlineStr">
         <is>
           <t>7.87</t>
         </is>
       </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>7.87</t>
-        </is>
-      </c>
       <c r="AP34" t="inlineStr">
         <is>
           <t>-13.15</t>
@@ -15064,20 +14868,16 @@
           <t>8582556.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>3897219.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>3897219.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>4486159.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>3463281.64</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>3463281.64</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>272001.502349861</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>8582556</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>8582556.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>128.2</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>134.8</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>125.54</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>125.54</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>12494.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>5302.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>5302.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>7547.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>17062.98</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>17062.98</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-4215.851280978359</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>12494</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>12494.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>126.7</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>134.52</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>125.14</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>134.52</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>125.14</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1602.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>4180.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>4180</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>7543.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>16993.14</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>16993.14</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-5033.729867838245</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1602</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1602.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>126.7</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>134.43</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>124.81</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>134.43</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>124.81</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>5142.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>5169.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>5169.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>10597.1</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>17207.26</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>17207.26</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-4855.351782358142</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>5142</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>5142.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>126.7</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>134.15</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>124.4</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>124.4</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>3277.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>7308.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>7308.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>15265.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>17495.64</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>17495.64</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-4806.406239445207</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>3277</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>3277.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>127.1</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>133.8</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>123.85</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>123.85</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>3998.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>7570.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>7570.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>21353.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>17673.18</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>17673.18</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-4365.005241017967</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>3998</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>3998.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>129.2</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>133.82</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>123.31</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>133.82</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>123.31</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>6881.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>9792.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>9792.200000000001</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>36873.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>17832.56</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>17832.56</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-3655.789341799842</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>6881</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>6881.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>132.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>133.82</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>122.79</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>133.82</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>122.79</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>6551.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>10907.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>10907.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>38280.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>17850.86</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>17850.86</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-2820.952723566814</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>6551</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>6551.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>134.2</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>133.72</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>122.11</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>133.72</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>122.11</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>15834.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>16024.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>16024.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>41189.4</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>17987.02</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>17987.02</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-1492.223528820818</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>15834</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>15834.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>136.4</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>133.3</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>121.33</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>121.33</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>4589.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>23222.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>23222.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>43498.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>17748.26</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>17748.26</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-535.3524102972151</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>4589</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>4589.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>140.9</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>132.68</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>120.51</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>132.68</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>120.51</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>15106.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>35135.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>35135.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>45753.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>17749.56</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>17749.56</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>2055.547487961398</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>15106</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>15106.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>144.9</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>131.72</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>119.6</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>131.72</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>119.6</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>12459.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>63955.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>63955.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>46039.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>17514.14</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>17514.14</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>4556.599218046511</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>12459</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>12459.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>16.61</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>16.76</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>16.56</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>16.56</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>53678.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-86543.32378675538</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>53678</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>53678.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>16.56</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>16.89</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>16.56</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>16.56</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>0</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-84262.13754565077</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>0</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>16.46</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>16.56</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>16.56</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2541.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>62247.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>62247.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>259666.2</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>311028.64</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>311028.64</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-84262.13754565077</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2541</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2541.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>16.36</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>16.55</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>37261.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>104754.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>104754.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>361872.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>316558.36</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>316558.36</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-75356.68463250968</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>37261</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>37261.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>16.3</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>16.53</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>5397.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>159612.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>159612.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>422513.7</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>318032.44</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>318032.44</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-63663.2988768614</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>5397</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>5397.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>16.36</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>16.53</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>263125.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>338180.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>338180.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>450006.7</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>321726.76</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>321726.76</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-41270.77283747599</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>263125</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>263125.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>16.32</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>16.52</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>16.52</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>2914.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>453442.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>453442.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>514657.9</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>319982.96</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>319982.96</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-35421.20803701546</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>2914</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>2914.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>16.32</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>16.52</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>16.52</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>215075.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>457084.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>457084.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>560695.4</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>335394.28</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>335394.28</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>2080.106250678713</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>215075</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>215075.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>16.4</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>16.5</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>311550.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>618991.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>618991.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>612835.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>399284.34</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>399284.34</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>32847.58715271752</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>311550</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>311550.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>16.54</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>16.47</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>16.47</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>898238.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>685415.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>685415.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>602375.8</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>401867.64</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>401867.64</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>65291.39604303311</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>898238</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>898238.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>16.61</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>16.45</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>839437.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>561833.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>561833</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>552519.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>398111.28</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>398111.28</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>46448.43031337566</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>839437</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>839437.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>56.42</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>56.35</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>56.75</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>56.75</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>463381.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1107514.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1107514.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1067531.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1307484.74</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1307484.74</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-104923.3115698104</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>463381</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>463381.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>56.23999999999999</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>56.32</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>56.76</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>56.76</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>1514061.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1185603.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1185603.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1043575.3</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1323758.44</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1323758.44</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-54076.64805658185</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>1514061</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>1514061.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>56.23999999999999</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>56.33</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>56.79</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>56.79</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>572851.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1068019.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1068019</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1137383.4</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1355329.06</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1355329.06</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-92080.10560709168</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>572851</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>572851.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>56.34</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>56.35</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>56.83</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>56.83</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1466052.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1092036.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1092036.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1650896.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1350369.16</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1350369.16</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-42238.25547899539</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1466052</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1466052.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>56.32000000000001</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>56.36</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>56.85</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>56.85</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1521229.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1086733.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1086733.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1566137.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1334093.2</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1334093.2</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-65227.21045746515</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1521229</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1521229.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>56.46</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>56.39</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>56.9</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>853825.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1027548.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1027548.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1510425.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1343468.66</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1343468.66</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-101650.8529103699</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>853825</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>853825.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>56.54</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>56.39</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>56.93</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>56.93</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>926138.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>901547.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>901547</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1543172.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1361157.66</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1361157.66</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-78546.66881057783</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>926138</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>926138.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>56.58000000000001</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>56.37</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>56.96</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>56.37</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>56.96</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>692937.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1206747.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1206747.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1479563.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1367191.1</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1367191.1</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-50483.27478192537</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>692937</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>692937.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>56.66</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>56.36</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>56.98</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>56.98</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>1439540.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>2209756.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>2209756.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1474607.4</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>1377872.8</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>1377872.8</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>16396.08364407555</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>1439540</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>1439540.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>56.54</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>56.34</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>57</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1225301.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>2045540.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>2045540.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1485671.1</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>1402124.58</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>1402124.58</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>31359.2712653596</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1225301</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1225301.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>56.4</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>56.32</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>57.03</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>57.03</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>223819.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1993303.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1993303.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1543619.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1423716.4</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1423716.4</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>74569.45817914582</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>223819</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>223819.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>21.74</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>22.72</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>22.72</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>298815.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1096677.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1096677</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>1104261.1</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>989539.84</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>989539.84</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-28989.25990078063</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>298815</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>298815.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>21.73</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>22.75</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>324798.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1213414.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1213414.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>1129377.0</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>1000495.3</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>1000495.3</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>35117.30167119089</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>324798</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>324798.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>21.73</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>22.79</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>22.79</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>957642.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1512953.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1512953.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>1186913.2</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>1018527.64</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>1018527.64</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>122660.0217143218</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>957642</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>957642.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>21.78</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>22.32</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>22.84</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>22.84</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>2110866.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1559553.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1559553</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>1209882.9</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>1009114.68</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>1009114.68</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>175535.6210004261</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>2110866</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>2110866.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>21.89</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>22.88</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>22.88</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>1791264.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1265233.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1265233</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>1058346.1</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>981059.28</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>981059.28</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>121243.3478019882</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>1791264</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>1791264.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>21.99</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>22.45</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>22.93</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>22.93</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>882504.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>1111845.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>1111845.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>959925.6</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>1009931.88</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>1009931.88</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>73595.90938272048</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>882504</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>882504.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>22.08</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>22.97</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>1822492.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>1045339.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>1045339.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>1055800.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>1005083.3</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>1005083.3</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>100266.8577343837</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>1822492</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>1822492.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>22.12</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>23.02</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>1190639.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>860872.8</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>860872.8</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>959040.1</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>997891.24</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>997891.24</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>34074.25331767462</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>1190639</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>1190639.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>22.17</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>22.61</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>23.06</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>639266.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>860212.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>860212.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>860843.4</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>991506.84</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>991506.84</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>5994.987961030332</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>639266</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>639266.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>22.21</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>22.64</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>23.09</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>23.09</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>1024325.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>851459.2</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>851459.2</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>859833.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>1004002.08</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>1004002.08</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>24743.3235957874</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>1024325</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>1024325.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>22.25</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>22.67</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>23.12</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>23.12</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>549974.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>808006.0</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>808006</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>794016.9</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>1000757.18</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>1000757.18</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>9386.648659876548</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>549974</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>549974.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>17.89</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>17.78</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>102091.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>279833.6</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>279833.6</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>470362.5</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>1001342.4</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>1001342.4</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-37497.86127596517</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>102091</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>102091.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>17.77</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>17.89</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>17.72</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>17.72</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>161861.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>323285.8</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>323285.8</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>476439.9</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>1012590.0</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>1012590</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-19461.3596436581</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>161861</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>161861.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>17.75</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>17.89</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>17.67</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>263052.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>356685.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>356685.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>484340.3</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>1018399.2</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>1018399.2</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>596.1912469112431</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>263052</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>263052.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>17.78</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>17.61</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>17.61</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>833469.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>444247.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>444247.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>465595.4</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>1018293.98</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>1018293.98</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>18386.64997462061</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>833469</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>833469.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>17.88</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>17.91</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>17.57</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>38695.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>594679.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>594679</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>388308.5</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1009136.1</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1009136.1</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-17971.18219917384</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>38695</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>38695.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>17.86</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>17.51</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>319352.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>660891.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>660891.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>419574.5</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>1013856.72</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>1013856.72</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>15885.24263109028</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>319352</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>319352.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>17.91</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>17.92</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>17.46</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>17.46</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>328860.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>629594.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>629594</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>409463.6</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>1012037.68</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>1012037.68</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>33613.84086607146</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>328860</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>328860.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>17.94</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>17.93</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>17.4</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>700862.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>611995.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>611995</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>388286.6</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>1014186.48</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>1014186.48</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>56721.20117082779</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>700862</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>700862.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>17.98</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>17.94</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>17.35</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>17.35</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>1585626.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>486943.2</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>486943.2</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>331234.0</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>1007151.98</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>1007151.98</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>47848.60156437865</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>1585626</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>1585626.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>17.94</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>17.94</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>17.29</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>17.29</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>369757.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>181938.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>181938</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>187266.6</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>984219.06</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>984219.0600000001</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-61331.56221499073</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>369757</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>369757.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>17.98</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>17.24</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>162865.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>178257.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>178257.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>172917.6</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>980798.52</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>980798.52</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-84841.13324926881</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>162865</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>162865.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>8.058</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>8.23</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>1896285.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>1640168.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>1640168.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>2074774.4</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>2745903.18</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>2745903.18</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-278196.5658211901</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>1896285</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>1896285.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>8.03</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>8.72</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>8.720000000000001</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>1018106.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>1666697.4</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>1666697.4</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>2208213.5</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>2798092.3</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>2798092.3</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-311909.246315005</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>1018106</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>1018106.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>8.026</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>8.27</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>8.75</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>8.75</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>1550247.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>2146559.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>2146559.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>2331238.9</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>2838047.06</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>2838047.06</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-254839.9953663475</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>1550247</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>1550247.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>8.064</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>8.77</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>2467759.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>2154473.6</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>2154473.6</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>2299822.3</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>2996852.04</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>2996852.04</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-221226.1727480385</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>2467759</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>2467759.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>8.124</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>8.34</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>1268447.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>2132057.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>2132057</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>2325063.6</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>2997985.44</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>2997985.44</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-263610.3485523104</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>1268447</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>1268447.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>8.208</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>8.38</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>8.82</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>8.82</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>2028928.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>2509380.0</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>2509380</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>2352087.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>3001246.5</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>3001246.5</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-186246.8015386881</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>2028928</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>2028928.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>8.254000000000001</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>8.41</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>8.84</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>3417417.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>2749729.6</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>2749729.6</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>2548398.8</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>3033280.84</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>3033280.84</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-150555.8843214172</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>3417417</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>3417417.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>8.264</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>8.86</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>8.859999999999999</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>1589817.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>2515918.2</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>2515918.2</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>2686804.7</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>2991212.52</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>2991212.52</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-242958.5424281219</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>1589817</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>1589817.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>8.251999999999999</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>8.48</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>8.88</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>8.880000000000001</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>2355676.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>2445171.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>2445171</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>2722123.7</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>3007183.3</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>3007183.3</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-170470.9632081245</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>2355676</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>2355676.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>8.254</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>8.51</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>8.9</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>3155062.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>2518070.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>2518070.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>3015119.6</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>3005306.64</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>3005306.64</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-142885.3513506949</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>3155062</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>3155062.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>8.222</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>8.52</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>8.92</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>8.92</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>3230676.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>2194794.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>2194794</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>3333753.8</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>2983606.78</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>2983606.78</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-184022.7861489849</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>3230676</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>3230676.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>28.62</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>25.17</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>0</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>0</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-45.99979809793327</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>0</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>27.52</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>24.88</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>25.17</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>28.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>0</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>0</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-45.99979809793327</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>28</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>26.42</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>25.17</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>10.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>0</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>0</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-49.37430700129521</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>10</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>25.28</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>24.54</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>25.17</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>0</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>0</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-49.18317858312919</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>0</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>24.14</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>24.36</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>25.2</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>34.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>0</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>0</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-49.18317858312919</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>34</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>24.18</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>25.23</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>0</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>0</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-43.35892299461874</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>0</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>24.29</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>25.38</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>25.38</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>0</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>0</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-43.35892299461874</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>0</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>25.51</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>0</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>0</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-43.35892299461874</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>0</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>24.51</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>25.62</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>0</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>0</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-43.35892299461874</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>0</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>24.62</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>25.74</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>25.74</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>0</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>0</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-43.35892299461874</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>1</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>23.43</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>25.86</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>0</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>0</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-22.01354819928218</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>0</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>48.88</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>48.07</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>48.07</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>1882.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>1903.4</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>1903.4</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>1878.8</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>2078.92</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>2078.92</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-21.47969704916932</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>1882</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>1882.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>48.89</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>48.04</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>48.04</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>2299.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>1599.4</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>1599.4</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>2254.1</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>2085.58</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>2085.58</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-20.77434434782913</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>2299</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>2299.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>48.85</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>48.74</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>48.01</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>48.01</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>1965.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>1372.4</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>1372.4</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>2310.4</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>2091.12</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>2091.12</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-63.70332819063447</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>1965</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>1965.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>48.97</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>48</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>1511.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>1266.8</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>1266.8</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>2403.2</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>2095.86</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>2095.86</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-86.96961481640528</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>1511</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>1511.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>49.12</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>48.62</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>47.96</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>47.96</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>1860.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>1590.4</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>1590.4</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>2378.4</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>2106.0</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>2106</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-68.45825232406355</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>1860</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>1860.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>49.23999999999999</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>48.54</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>47.93</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>47.93</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>362.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>1854.2</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>1854.2</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>2252.2</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>2078.68</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>2078.68</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>-76.96136832342995</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>362</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>362.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>49.45999999999999</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>48.46</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>47.9</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>47.9</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>1164.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>2908.8</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>2908.8</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>2314.3</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>2094.78</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>2094.78</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>74.13994340331146</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>1164</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>1164.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>49.54000000000001</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>47.87</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>47.87</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>1437.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>3248.4</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>3248.4</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>2443.7</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>2099.04</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>2099.04</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>201.4225336056816</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>1437</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>1437.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>49.58</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>48.36</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>47.84</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>48.36</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>47.84</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>3129.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>3539.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>3539.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>2402.8</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>2080.8</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>2080.8</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>346.8111434088642</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>3129</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>3129.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>49.43</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>48.24</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>47.79</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>47.79</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>3179.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>3166.4</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>3166.4</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>2213.0</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>2070.76</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>2070.76</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>360.8373308630944</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>3179</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>3179.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>49.21</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>48.13</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>47.76</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>47.76</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>5635.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>2650.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>2650.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>1998.3</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>2043.9</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>2043.9</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>362.6305511240266</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>5635</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>5635.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>403535423</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>363440217</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>451484020</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>569640781</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>1056628890</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>436450840</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>365688993</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>676579414</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>622810797</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>566992376</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>832928036</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58425,7 +57633,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -58609,15 +57817,11 @@
           <t>34.14</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>34.28</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>35.67</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58664,20 +57868,16 @@
           <t>703729.0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>832338.4</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>832338.4</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>1365486.3</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>2770195.72</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>2770195.72</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57894,10 @@
           <t>-407242.1677682393</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>703729</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>703729.0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
@@ -58861,7 +58063,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -59045,15 +58247,11 @@
           <t>34.05</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>34.34</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>35.73</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>35.73</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -59100,20 +58298,16 @@
           <t>811272.0</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>1025107.0</t>
-        </is>
+      <c r="AX135" t="n">
+        <v>1025107</v>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>1422951.5</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>2781982.36</t>
-        </is>
+      <c r="AZ135" t="n">
+        <v>2781982.36</v>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
@@ -59130,8 +58324,10 @@
           <t>-397836.2898797004</t>
         </is>
       </c>
-      <c r="BD135" t="n">
-        <v>811272</v>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>811272.0</t>
+        </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
@@ -59297,7 +58493,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -59481,15 +58677,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>34.42</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>35.78</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>35.78</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59536,20 +58728,16 @@
           <t>1487179.0</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>1339575.6</t>
-        </is>
+      <c r="AX136" t="n">
+        <v>1339575.6</v>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>1890505.4</t>
         </is>
       </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>2785701.92</t>
-        </is>
+      <c r="AZ136" t="n">
+        <v>2785701.92</v>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
@@ -59566,8 +58754,10 @@
           <t>-381713.3468289413</t>
         </is>
       </c>
-      <c r="BD136" t="n">
-        <v>1487179</v>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>1487179.0</t>
+        </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
@@ -59733,7 +58923,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59917,15 +59107,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>35.84</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59972,20 +59158,16 @@
           <t>582054.0</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>1655590.0</t>
-        </is>
+      <c r="AX137" t="n">
+        <v>1655590</v>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>2092838.2</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>2769787.1</t>
-        </is>
+      <c r="AZ137" t="n">
+        <v>2769787.1</v>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
@@ -60002,8 +59184,10 @@
           <t>-417466.5586553942</t>
         </is>
       </c>
-      <c r="BD137" t="n">
-        <v>582054</v>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>582054.0</t>
+        </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
@@ -60169,7 +59353,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -60353,15 +59537,11 @@
           <t>33.92999999999999</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>34.57</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>35.9</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -60408,20 +59588,16 @@
           <t>577458.0</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>1688519.2</t>
-        </is>
+      <c r="AX138" t="n">
+        <v>1688519.2</v>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>2334206.6</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>2765629.48</t>
-        </is>
+      <c r="AZ138" t="n">
+        <v>2765629.48</v>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
@@ -60438,8 +59614,10 @@
           <t>-356655.3770269202</t>
         </is>
       </c>
-      <c r="BD138" t="n">
-        <v>577458</v>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>577458.0</t>
+        </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
@@ -60605,7 +59783,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -60789,15 +59967,11 @@
           <t>33.93</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>34.66</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>35.97</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>35.97</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60844,20 +60018,16 @@
           <t>1667572.0</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>1898634.2</t>
-        </is>
+      <c r="AX139" t="n">
+        <v>1898634.2</v>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>2466923.8</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>2771121.32</t>
-        </is>
+      <c r="AZ139" t="n">
+        <v>2771121.32</v>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
@@ -60874,8 +60044,10 @@
           <t>-256552.1398067102</t>
         </is>
       </c>
-      <c r="BD139" t="n">
-        <v>1667572</v>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>1667572.0</t>
+        </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
@@ -61041,7 +60213,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -61225,15 +60397,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>34.74</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>36.03</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>36.03</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -61280,20 +60448,16 @@
           <t>2383615.0</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>1820796.0</t>
-        </is>
+      <c r="AX140" t="n">
+        <v>1820796</v>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>2506266.8</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>2754839.88</t>
-        </is>
+      <c r="AZ140" t="n">
+        <v>2754839.88</v>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
@@ -61310,8 +60474,10 @@
           <t>-221182.8673561704</t>
         </is>
       </c>
-      <c r="BD140" t="n">
-        <v>2383615</v>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>2383615.0</t>
+        </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
@@ -61477,7 +60643,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -61661,15 +60827,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>34.83</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61716,20 +60878,16 @@
           <t>3067251.0</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>2441435.2</t>
-        </is>
+      <c r="AX141" t="n">
+        <v>2441435.2</v>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>2486763.3</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>2745284.78</t>
-        </is>
+      <c r="AZ141" t="n">
+        <v>2745284.78</v>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
@@ -61746,8 +60904,10 @@
           <t>-239474.8400212508</t>
         </is>
       </c>
-      <c r="BD141" t="n">
-        <v>3067251</v>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>3067251.0</t>
+        </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
@@ -61913,7 +61073,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -62097,15 +61257,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>36.15</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -62152,20 +61308,16 @@
           <t>746700.0</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>2530086.4</t>
-        </is>
+      <c r="AX142" t="n">
+        <v>2530086.4</v>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>2848651.5</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
-        <is>
-          <t>2788241.7</t>
-        </is>
+      <c r="AZ142" t="n">
+        <v>2788241.7</v>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
@@ -62182,8 +61334,10 @@
           <t>-330300.2709706062</t>
         </is>
       </c>
-      <c r="BD142" t="n">
-        <v>746700</v>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>746700.0</t>
+        </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
@@ -62349,7 +61503,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -62533,15 +61687,11 @@
           <t>34.08</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>36.21</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62588,20 +61738,16 @@
           <t>1628033.0</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>2979894.0</t>
-        </is>
+      <c r="AX143" t="n">
+        <v>2979894</v>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>3115544.6</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
-        <is>
-          <t>2857333.8</t>
-        </is>
+      <c r="AZ143" t="n">
+        <v>2857333.8</v>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
@@ -62618,8 +61764,10 @@
           <t>-199623.9840778778</t>
         </is>
       </c>
-      <c r="BD143" t="n">
-        <v>1628033</v>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>1628033.0</t>
+        </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
@@ -62785,7 +61933,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -62969,15 +62117,11 @@
           <t>34.17</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>35.12</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>36.27</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>36.27</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -63024,20 +62168,16 @@
           <t>1278381.0</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>3035213.4</t>
-        </is>
+      <c r="AX144" t="n">
+        <v>3035213.4</v>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>3208352.2</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>2902801.48</t>
-        </is>
+      <c r="AZ144" t="n">
+        <v>2902801.48</v>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
@@ -63054,8 +62194,10 @@
           <t>-100242.6819426282</t>
         </is>
       </c>
-      <c r="BD144" t="n">
-        <v>1278381</v>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>1278381.0</t>
+        </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
